--- a/حركة التشغيل.xlsx
+++ b/حركة التشغيل.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\backoup\25-2-2026\حركة التشغيل\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\backoup\25-2-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96DD73B0-EEB7-4916-B73F-516128318F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08030D5A-BD58-43A6-81D4-A2EF83863D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="85">
   <si>
     <t>رقم الرسالة</t>
   </si>
@@ -53,9 +53,6 @@
     <t>بوكسر ذبدة</t>
   </si>
   <si>
-    <t>over</t>
-  </si>
-  <si>
     <t>M</t>
   </si>
   <si>
@@ -77,9 +74,6 @@
     <t>L</t>
   </si>
   <si>
-    <t xml:space="preserve">حروف قديمة </t>
-  </si>
-  <si>
     <t>S</t>
   </si>
   <si>
@@ -104,12 +98,6 @@
     <t>طقم بوكسر بناتي</t>
   </si>
   <si>
-    <t>كاش ½ كم طويل</t>
-  </si>
-  <si>
-    <t>طويل</t>
-  </si>
-  <si>
     <t>تاريخ القص</t>
   </si>
   <si>
@@ -128,18 +116,6 @@
     <t>اندر مطبوع</t>
   </si>
   <si>
-    <t>228 A</t>
-  </si>
-  <si>
-    <t>228 B</t>
-  </si>
-  <si>
-    <t>229 A</t>
-  </si>
-  <si>
-    <t>229 B</t>
-  </si>
-  <si>
     <t>230 A</t>
   </si>
   <si>
@@ -161,30 +137,12 @@
     <t>اوفر</t>
   </si>
   <si>
-    <t xml:space="preserve">بدلة بناتي قطن 1 2 3 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 2 3 </t>
-  </si>
-  <si>
-    <t>بدلة بناتي قطن 4 6 8</t>
-  </si>
-  <si>
     <t>4 6 8</t>
   </si>
   <si>
     <t>حروف صغيرة</t>
   </si>
   <si>
-    <t>عباية بناتي</t>
-  </si>
-  <si>
-    <t>صورة</t>
-  </si>
-  <si>
-    <t>عباية بناتي صيفي</t>
-  </si>
-  <si>
     <t>بدلة اولادي قطن 1 2 3</t>
   </si>
   <si>
@@ -200,9 +158,6 @@
     <t>جامبو</t>
   </si>
   <si>
-    <t>شورت رجالي مقلم</t>
-  </si>
-  <si>
     <t>عباية حريمي ½ كم جامبو</t>
   </si>
   <si>
@@ -213,6 +168,129 @@
   </si>
   <si>
     <t>صدر دبدوب</t>
+  </si>
+  <si>
+    <t>159 A</t>
+  </si>
+  <si>
+    <t>57 A</t>
+  </si>
+  <si>
+    <t>37 A</t>
+  </si>
+  <si>
+    <t>39 B</t>
+  </si>
+  <si>
+    <t>52 B</t>
+  </si>
+  <si>
+    <t>53 B</t>
+  </si>
+  <si>
+    <t>54 B</t>
+  </si>
+  <si>
+    <t>55 B</t>
+  </si>
+  <si>
+    <t>56 B</t>
+  </si>
+  <si>
+    <t>38 A</t>
+  </si>
+  <si>
+    <t>39 A</t>
+  </si>
+  <si>
+    <t>38 B</t>
+  </si>
+  <si>
+    <t>بدي</t>
+  </si>
+  <si>
+    <t>اولادي ذبدة</t>
+  </si>
+  <si>
+    <t>حروف قديمة</t>
+  </si>
+  <si>
+    <t>حروف كبيرة</t>
+  </si>
+  <si>
+    <t>صدر ارنب</t>
+  </si>
+  <si>
+    <t>بدلة شماعة بناتي 1&amp;2&amp;3</t>
+  </si>
+  <si>
+    <t>بيجامة بناتي صيفي صورة</t>
+  </si>
+  <si>
+    <t>طقم بكسر ميكي</t>
+  </si>
+  <si>
+    <t>برامودا حريمي مشجر</t>
+  </si>
+  <si>
+    <t>مقاسات</t>
+  </si>
+  <si>
+    <t>6XL</t>
+  </si>
+  <si>
+    <t>7XL</t>
+  </si>
+  <si>
+    <t>كم تيجر</t>
+  </si>
+  <si>
+    <t>232 A</t>
+  </si>
+  <si>
+    <t>بدلة اولادي قطن 10 12 14</t>
+  </si>
+  <si>
+    <t>10 12 14</t>
+  </si>
+  <si>
+    <t>232 B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عباية جامبو طباعة صدر وظهر </t>
+  </si>
+  <si>
+    <t>حريمي</t>
+  </si>
+  <si>
+    <t>34 A</t>
+  </si>
+  <si>
+    <t>34 B</t>
+  </si>
+  <si>
+    <t>36 B</t>
+  </si>
+  <si>
+    <t>37 B</t>
+  </si>
+  <si>
+    <t>كمر تيجر</t>
+  </si>
+  <si>
+    <t>طقم بوكسر قطن جديد اولادي</t>
+  </si>
+  <si>
+    <t>35 A</t>
+  </si>
+  <si>
+    <t>كت</t>
+  </si>
+  <si>
+    <t>صدر ارنب و فروالة</t>
+  </si>
+  <si>
+    <t>35 B</t>
   </si>
 </sst>
 </file>
@@ -222,12 +300,20 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="178"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -294,28 +380,31 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{77E0CB78-3F28-42BA-BF0C-342C7ADE2EAD}"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{9A42A7F6-CD71-402C-ABBE-68D5377A81E5}"/>
     <cellStyle name="Normal 4" xfId="3" xr:uid="{2A8A7AFE-CBDE-4B4C-84A8-F47728DB6D35}"/>
+    <cellStyle name="Normal 5" xfId="4" xr:uid="{FC7BDFA3-D05E-4C0D-A0CC-602038970297}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -593,22 +682,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -617,1572 +706,3532 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>46057</v>
+        <v>45721</v>
       </c>
       <c r="B2">
-        <v>433</v>
+        <v>217</v>
       </c>
       <c r="C2">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" t="s">
-        <v>7</v>
+        <v>40</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>323</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>46057</v>
+        <v>45845</v>
       </c>
       <c r="B3">
-        <v>433</v>
-      </c>
-      <c r="C3">
-        <v>17</v>
+        <v>280</v>
+      </c>
+      <c r="C3" t="s">
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="G3" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="H3">
-        <v>323</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>46057</v>
+        <v>45845</v>
       </c>
       <c r="B4">
-        <v>433</v>
-      </c>
-      <c r="C4">
-        <v>18</v>
+        <v>280</v>
+      </c>
+      <c r="C4" t="s">
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="H4">
-        <v>323</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>46060</v>
+        <v>45845</v>
       </c>
       <c r="B5">
-        <v>438</v>
-      </c>
-      <c r="C5">
-        <v>17</v>
+        <v>280</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
       </c>
       <c r="E5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="G5" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="H5">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>46077</v>
+        <v>45836</v>
       </c>
       <c r="B6">
-        <v>445</v>
-      </c>
-      <c r="C6">
-        <v>15</v>
+        <v>273</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H6">
-        <v>420</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>46077</v>
+        <v>45992</v>
       </c>
       <c r="B7">
-        <v>445</v>
-      </c>
-      <c r="C7">
-        <v>18</v>
+        <v>402</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="H7">
-        <v>513</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>46077</v>
+        <v>46060</v>
       </c>
       <c r="B8">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="C8">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H8">
-        <v>360</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>46079</v>
+        <v>46094</v>
       </c>
       <c r="B9">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="C9">
-        <v>208</v>
+        <v>136</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>5</v>
       </c>
       <c r="H9">
-        <v>68.5</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>46079</v>
+        <v>46095</v>
       </c>
       <c r="B10">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="C10">
-        <v>209</v>
+        <v>138</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10">
-        <v>4</v>
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>6</v>
       </c>
       <c r="H10">
-        <v>68.5</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>46079</v>
+        <v>46098</v>
       </c>
       <c r="B11">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="C11">
-        <v>210</v>
+        <v>142</v>
+      </c>
+      <c r="D11" t="s">
+        <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="G11" t="s">
+        <v>18</v>
       </c>
       <c r="H11">
-        <v>68.5</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>46079</v>
+        <v>46126</v>
       </c>
       <c r="B12">
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="C12">
-        <v>211</v>
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
         <v>8</v>
       </c>
       <c r="H12">
-        <v>68.5</v>
+        <v>440</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>46079</v>
+        <v>46154</v>
       </c>
       <c r="B13">
-        <v>450</v>
+        <v>495</v>
       </c>
       <c r="C13">
-        <v>212</v>
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13">
-        <v>10</v>
+        <v>34</v>
+      </c>
+      <c r="G13" t="s">
+        <v>7</v>
       </c>
       <c r="H13">
-        <v>68.5</v>
+        <v>521</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>46079</v>
+        <v>46154</v>
       </c>
       <c r="B14">
-        <v>450</v>
+        <v>495</v>
       </c>
       <c r="C14">
-        <v>213</v>
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14">
-        <v>12</v>
+        <v>34</v>
+      </c>
+      <c r="G14" t="s">
+        <v>8</v>
       </c>
       <c r="H14">
-        <v>68.5</v>
+        <v>521</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>46079</v>
+        <v>46162</v>
       </c>
       <c r="B15">
-        <v>451</v>
-      </c>
-      <c r="C15">
-        <v>208</v>
+        <v>499</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
+        <v>37</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
+        <v>33</v>
       </c>
       <c r="H15">
-        <v>31.5</v>
+        <v>450</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>46079</v>
+        <v>46163</v>
       </c>
       <c r="B16">
-        <v>451</v>
-      </c>
-      <c r="C16">
-        <v>209</v>
+        <v>500</v>
+      </c>
+      <c r="C16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16">
-        <v>4</v>
+        <v>37</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
+        <v>33</v>
       </c>
       <c r="H16">
-        <v>31.5</v>
+        <v>450</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>46079</v>
+        <v>46163</v>
       </c>
       <c r="B17">
-        <v>451</v>
-      </c>
-      <c r="C17">
-        <v>210</v>
+        <v>500</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17">
-        <v>6</v>
+        <v>37</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17" t="s">
+        <v>33</v>
       </c>
       <c r="H17">
-        <v>31.5</v>
+        <v>450</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>46079</v>
+        <v>46177</v>
       </c>
       <c r="B18">
-        <v>451</v>
+        <v>508</v>
       </c>
       <c r="C18">
-        <v>211</v>
+        <v>18</v>
+      </c>
+      <c r="D18" t="s">
+        <v>10</v>
       </c>
       <c r="E18" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18">
+        <v>10</v>
+      </c>
+      <c r="G18" t="s">
         <v>8</v>
       </c>
       <c r="H18">
-        <v>31.5</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>46079</v>
+        <v>46181</v>
       </c>
       <c r="B19">
-        <v>451</v>
+        <v>511</v>
       </c>
       <c r="C19">
-        <v>212</v>
+        <v>40</v>
+      </c>
+      <c r="D19" t="s">
+        <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
       </c>
-      <c r="G19">
-        <v>10</v>
+      <c r="G19" t="s">
+        <v>7</v>
       </c>
       <c r="H19">
-        <v>31.5</v>
+        <v>415</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>46079</v>
+        <v>46181</v>
       </c>
       <c r="B20">
-        <v>451</v>
+        <v>511</v>
       </c>
       <c r="C20">
-        <v>213</v>
+        <v>41</v>
+      </c>
+      <c r="D20" t="s">
+        <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
       </c>
-      <c r="G20">
-        <v>12</v>
+      <c r="G20" t="s">
+        <v>8</v>
       </c>
       <c r="H20">
-        <v>31.5</v>
+        <v>415</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>46094</v>
+        <v>46181</v>
       </c>
       <c r="B21">
-        <v>458</v>
+        <v>511</v>
       </c>
       <c r="C21">
-        <v>136</v>
+        <v>42</v>
+      </c>
+      <c r="D21" t="s">
+        <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+      <c r="F21" t="s">
+        <v>16</v>
       </c>
       <c r="G21" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H21">
-        <v>326</v>
+        <v>415</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>46095</v>
+        <v>46181</v>
       </c>
       <c r="B22">
-        <v>459</v>
+        <v>511</v>
       </c>
       <c r="C22">
-        <v>138</v>
+        <v>43</v>
+      </c>
+      <c r="D22" t="s">
+        <v>16</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F22" t="s">
         <v>16</v>
       </c>
       <c r="G22" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H22">
-        <v>266</v>
+        <v>345</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>46098</v>
+        <v>46181</v>
       </c>
       <c r="B23">
-        <v>462</v>
+        <v>511</v>
       </c>
       <c r="C23">
-        <v>142</v>
+        <v>44</v>
+      </c>
+      <c r="D23" t="s">
+        <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F23" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="H23">
-        <v>288</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>46116</v>
+        <v>46185</v>
       </c>
       <c r="B24">
-        <v>469</v>
-      </c>
-      <c r="C24">
-        <v>31</v>
+        <v>509</v>
+      </c>
+      <c r="C24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
-      </c>
-      <c r="F24" t="s">
-        <v>39</v>
+        <v>35</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="H24">
-        <v>805</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>46126</v>
+        <v>46185</v>
       </c>
       <c r="B25">
-        <v>476</v>
-      </c>
-      <c r="C25">
-        <v>18</v>
+        <v>509</v>
+      </c>
+      <c r="C25" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F25" t="s">
-        <v>40</v>
+        <v>35</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="H25">
-        <v>440</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <v>46135</v>
+        <v>46185</v>
       </c>
       <c r="B26">
-        <v>478</v>
-      </c>
-      <c r="C26">
-        <v>15</v>
+        <v>509</v>
+      </c>
+      <c r="C26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>4</v>
-      </c>
-      <c r="F26" t="s">
-        <v>40</v>
+        <v>35</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="H26">
-        <v>383</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>46135</v>
+        <v>46185</v>
       </c>
       <c r="B27">
-        <v>478</v>
-      </c>
-      <c r="C27">
-        <v>16</v>
+        <v>514</v>
+      </c>
+      <c r="C27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" t="s">
+        <v>43</v>
       </c>
       <c r="E27" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G27" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H27">
-        <v>412</v>
+        <v>385</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>46135</v>
+        <v>46185</v>
       </c>
       <c r="B28">
-        <v>478</v>
-      </c>
-      <c r="C28">
-        <v>17</v>
+        <v>514</v>
+      </c>
+      <c r="C28" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" t="s">
+        <v>43</v>
       </c>
       <c r="E28" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G28" t="s">
         <v>8</v>
       </c>
       <c r="H28">
-        <v>536</v>
+        <v>525</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <v>46135</v>
+        <v>46195</v>
       </c>
       <c r="B29">
-        <v>478</v>
-      </c>
-      <c r="C29">
-        <v>17</v>
+        <v>518</v>
+      </c>
+      <c r="C29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" t="s">
-        <v>40</v>
+        <v>62</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H29">
-        <v>385</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <v>46135</v>
+        <v>46195</v>
       </c>
       <c r="B30">
-        <v>478</v>
-      </c>
-      <c r="C30">
-        <v>18</v>
+        <v>518</v>
+      </c>
+      <c r="C30" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>4</v>
-      </c>
-      <c r="F30" t="s">
-        <v>40</v>
+        <v>62</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H30">
-        <v>385</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <v>46147</v>
+        <v>46195</v>
       </c>
       <c r="B31">
-        <v>491</v>
+        <v>518</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>50</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>41</v>
+        <v>62</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H31">
-        <v>477</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
-        <v>46147</v>
+        <v>46195</v>
       </c>
       <c r="B32">
-        <v>491</v>
+        <v>518</v>
       </c>
       <c r="C32" t="s">
-        <v>31</v>
+        <v>51</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>41</v>
+        <v>62</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="H32">
-        <v>477</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
-        <v>46147</v>
+        <v>46195</v>
       </c>
       <c r="B33">
-        <v>491</v>
+        <v>518</v>
       </c>
       <c r="C33" t="s">
-        <v>32</v>
+        <v>52</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>43</v>
+        <v>62</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="H33">
-        <v>477</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
-        <v>46147</v>
+        <v>46195</v>
       </c>
       <c r="B34">
-        <v>491</v>
-      </c>
-      <c r="C34" t="s">
-        <v>33</v>
+        <v>520</v>
+      </c>
+      <c r="C34" s="5">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D34" t="s">
+        <v>57</v>
       </c>
       <c r="E34" t="s">
-        <v>43</v>
+        <v>63</v>
+      </c>
+      <c r="F34" t="s">
+        <v>57</v>
       </c>
       <c r="G34" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="H34">
-        <v>477</v>
+        <v>440</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
-        <v>46154</v>
+        <v>46197</v>
       </c>
       <c r="B35">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="C35">
         <v>15</v>
       </c>
+      <c r="D35" t="s">
+        <v>58</v>
+      </c>
       <c r="E35" t="s">
         <v>4</v>
       </c>
       <c r="F35" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="G35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H35">
-        <v>300</v>
+        <v>320</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
-        <v>46154</v>
+        <v>46197</v>
       </c>
       <c r="B36">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="C36">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="D36" t="s">
+        <v>58</v>
       </c>
       <c r="E36" t="s">
         <v>4</v>
       </c>
       <c r="F36" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="G36" t="s">
         <v>7</v>
       </c>
       <c r="H36">
-        <v>447</v>
+        <v>490</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
-        <v>46154</v>
+        <v>46197</v>
       </c>
       <c r="B37">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="C37">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="D37" t="s">
+        <v>58</v>
       </c>
       <c r="E37" t="s">
         <v>4</v>
       </c>
       <c r="F37" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="G37" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H37">
-        <v>521</v>
+        <v>420</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
-        <v>46154</v>
+        <v>46197</v>
       </c>
       <c r="B38">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="C38">
         <v>18</v>
       </c>
+      <c r="D38" t="s">
+        <v>58</v>
+      </c>
       <c r="E38" t="s">
         <v>4</v>
       </c>
       <c r="F38" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="G38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H38">
-        <v>521</v>
+        <v>320</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
-        <v>46156</v>
+        <v>46199</v>
       </c>
       <c r="B39">
-        <v>496</v>
+        <v>524</v>
       </c>
       <c r="C39">
         <v>42</v>
       </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
       <c r="E39" t="s">
-        <v>29</v>
-      </c>
-      <c r="F39" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H39">
-        <v>433</v>
+        <v>447.5</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
-        <v>46156</v>
+        <v>46199</v>
       </c>
       <c r="B40">
-        <v>496</v>
+        <v>524</v>
       </c>
       <c r="C40">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>29</v>
-      </c>
-      <c r="F40" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="H40">
-        <v>433</v>
+        <v>447.5</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
-        <v>46161</v>
+        <v>46204</v>
       </c>
       <c r="B41">
-        <v>498</v>
+        <v>522</v>
       </c>
       <c r="C41">
-        <v>66</v>
+        <v>28</v>
+      </c>
+      <c r="D41" t="s">
+        <v>31</v>
       </c>
       <c r="E41" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="F41" t="s">
-        <v>47</v>
-      </c>
-      <c r="G41">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="G41" t="s">
+        <v>5</v>
       </c>
       <c r="H41">
-        <v>240</v>
+        <v>385</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
-        <v>46161</v>
+        <v>46204</v>
       </c>
       <c r="B42">
-        <v>498</v>
+        <v>522</v>
       </c>
       <c r="C42">
-        <v>67</v>
+        <v>29</v>
+      </c>
+      <c r="D42" t="s">
+        <v>31</v>
       </c>
       <c r="E42" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="F42" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="G42" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H42">
-        <v>240</v>
+        <v>741</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
-        <v>46161</v>
+        <v>46204</v>
       </c>
       <c r="B43">
-        <v>498</v>
+        <v>522</v>
       </c>
       <c r="C43">
-        <v>68</v>
+        <v>30</v>
+      </c>
+      <c r="D43" t="s">
+        <v>31</v>
       </c>
       <c r="E43" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="F43" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="G43" t="s">
         <v>6</v>
       </c>
       <c r="H43">
-        <v>270</v>
+        <v>741</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
-        <v>46161</v>
+        <v>46204</v>
       </c>
       <c r="B44">
-        <v>498</v>
+        <v>522</v>
       </c>
       <c r="C44">
-        <v>69</v>
+        <v>31</v>
+      </c>
+      <c r="D44" t="s">
+        <v>31</v>
       </c>
       <c r="E44" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="F44" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="G44" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H44">
-        <v>270</v>
+        <v>833</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
-        <v>46161</v>
+        <v>46204</v>
       </c>
       <c r="B45">
-        <v>498</v>
+        <v>522</v>
       </c>
       <c r="C45">
-        <v>70</v>
+        <v>32</v>
+      </c>
+      <c r="D45" t="s">
+        <v>31</v>
       </c>
       <c r="E45" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="F45" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="G45" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H45">
-        <v>270</v>
+        <v>833</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
-        <v>46161</v>
+        <v>46205</v>
       </c>
       <c r="B46">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="C46">
-        <v>71</v>
+        <v>29</v>
+      </c>
+      <c r="D46" t="s">
+        <v>31</v>
       </c>
       <c r="E46" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="F46" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="G46" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H46">
-        <v>270</v>
+        <v>741</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
-        <v>46161</v>
+        <v>46203</v>
       </c>
       <c r="B47">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="C47">
-        <v>72</v>
+        <v>14</v>
+      </c>
+      <c r="D47" t="s">
+        <v>59</v>
       </c>
       <c r="E47" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="F47" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="G47" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H47">
-        <v>270</v>
+        <v>188</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
-        <v>46162</v>
+        <v>46203</v>
       </c>
       <c r="B48">
-        <v>499</v>
-      </c>
-      <c r="C48" t="s">
-        <v>34</v>
+        <v>526</v>
+      </c>
+      <c r="C48">
+        <v>16</v>
+      </c>
+      <c r="D48" t="s">
+        <v>59</v>
       </c>
       <c r="E48" t="s">
-        <v>49</v>
+        <v>4</v>
+      </c>
+      <c r="F48" t="s">
+        <v>59</v>
       </c>
       <c r="G48" t="s">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="H48">
-        <v>450</v>
+        <v>433</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
-        <v>46162</v>
+        <v>46203</v>
       </c>
       <c r="B49">
-        <v>499</v>
-      </c>
-      <c r="C49" t="s">
-        <v>35</v>
+        <v>526</v>
+      </c>
+      <c r="C49">
+        <v>17</v>
+      </c>
+      <c r="D49" t="s">
+        <v>59</v>
       </c>
       <c r="E49" t="s">
-        <v>49</v>
+        <v>4</v>
+      </c>
+      <c r="F49" t="s">
+        <v>59</v>
       </c>
       <c r="G49" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="H49">
-        <v>450</v>
+        <v>466.5</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
-        <v>46162</v>
+        <v>46203</v>
       </c>
       <c r="B50">
-        <v>499</v>
-      </c>
-      <c r="C50" t="s">
-        <v>36</v>
+        <v>526</v>
+      </c>
+      <c r="C50">
+        <v>18</v>
+      </c>
+      <c r="D50" t="s">
+        <v>59</v>
       </c>
       <c r="E50" t="s">
-        <v>51</v>
+        <v>4</v>
+      </c>
+      <c r="F50" t="s">
+        <v>59</v>
       </c>
       <c r="G50" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="H50">
-        <v>450</v>
+        <v>466.5</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
-        <v>46162</v>
+        <v>46203</v>
       </c>
       <c r="B51">
-        <v>499</v>
-      </c>
-      <c r="C51" t="s">
-        <v>37</v>
+        <v>526</v>
+      </c>
+      <c r="C51">
+        <v>19</v>
+      </c>
+      <c r="D51" t="s">
+        <v>59</v>
       </c>
       <c r="E51" t="s">
-        <v>51</v>
+        <v>4</v>
+      </c>
+      <c r="F51" t="s">
+        <v>59</v>
       </c>
       <c r="G51" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="H51">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
-        <v>46163</v>
+        <v>46209</v>
       </c>
       <c r="B52">
-        <v>500</v>
-      </c>
-      <c r="C52" t="s">
-        <v>34</v>
+        <v>528</v>
+      </c>
+      <c r="C52">
+        <v>106</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>49</v>
+        <v>64</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="H52">
-        <v>450</v>
+        <v>415</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
-        <v>46163</v>
+        <v>46209</v>
       </c>
       <c r="B53">
-        <v>500</v>
-      </c>
-      <c r="C53" t="s">
-        <v>35</v>
+        <v>531</v>
+      </c>
+      <c r="C53">
+        <v>139</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>49</v>
+        <v>17</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="H53">
-        <v>450</v>
+        <v>204</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
-        <v>46163</v>
+        <v>46209</v>
       </c>
       <c r="B54">
+        <v>530</v>
+      </c>
+      <c r="C54">
+        <v>142</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H54">
         <v>500</v>
-      </c>
-      <c r="C54" t="s">
-        <v>36</v>
-      </c>
-      <c r="E54" t="s">
-        <v>51</v>
-      </c>
-      <c r="G54" t="s">
-        <v>44</v>
-      </c>
-      <c r="H54">
-        <v>450</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
-        <v>46163</v>
+        <v>46210</v>
       </c>
       <c r="B55">
-        <v>500</v>
+        <v>529</v>
       </c>
       <c r="C55" t="s">
-        <v>37</v>
+        <v>53</v>
+      </c>
+      <c r="D55" t="s">
+        <v>60</v>
       </c>
       <c r="E55" t="s">
-        <v>51</v>
+        <v>19</v>
+      </c>
+      <c r="F55" t="s">
+        <v>60</v>
       </c>
       <c r="G55" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="H55">
-        <v>450</v>
+        <v>476</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
-        <v>46163</v>
+        <v>46210</v>
       </c>
       <c r="B56">
-        <v>501</v>
+        <v>529</v>
       </c>
       <c r="C56" t="s">
-        <v>38</v>
+        <v>54</v>
+      </c>
+      <c r="D56" t="s">
+        <v>60</v>
       </c>
       <c r="E56" t="s">
-        <v>52</v>
+        <v>19</v>
+      </c>
+      <c r="F56" t="s">
+        <v>60</v>
       </c>
       <c r="G56" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="H56">
-        <v>366</v>
+        <v>476</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
-        <v>46165</v>
+        <v>46210</v>
       </c>
       <c r="B57">
-        <v>502</v>
-      </c>
-      <c r="C57">
-        <v>100</v>
+        <v>529</v>
+      </c>
+      <c r="C57" t="s">
+        <v>55</v>
+      </c>
+      <c r="D57" t="s">
+        <v>60</v>
       </c>
       <c r="E57" t="s">
-        <v>54</v>
+        <v>19</v>
+      </c>
+      <c r="F57" t="s">
+        <v>60</v>
       </c>
       <c r="G57" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H57">
-        <v>540</v>
+        <v>510</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
-        <v>46165</v>
+        <v>46210</v>
       </c>
       <c r="B58">
-        <v>502</v>
-      </c>
-      <c r="C58">
-        <v>101</v>
+        <v>529</v>
+      </c>
+      <c r="C58" t="s">
+        <v>47</v>
+      </c>
+      <c r="D58" t="s">
+        <v>60</v>
       </c>
       <c r="E58" t="s">
-        <v>54</v>
+        <v>19</v>
+      </c>
+      <c r="F58" t="s">
+        <v>60</v>
       </c>
       <c r="G58" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H58">
-        <v>675</v>
+        <v>510</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
-        <v>46165</v>
+        <v>46211</v>
       </c>
       <c r="B59">
-        <v>502</v>
+        <v>532</v>
       </c>
       <c r="C59">
-        <v>102</v>
+        <v>144</v>
+      </c>
+      <c r="D59" t="s">
+        <v>14</v>
       </c>
       <c r="E59" t="s">
-        <v>54</v>
+        <v>17</v>
+      </c>
+      <c r="F59" t="s">
+        <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="H59">
-        <v>675</v>
+        <v>375</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
-        <v>46165</v>
+        <v>46212</v>
       </c>
       <c r="B60">
-        <v>503</v>
+        <v>533</v>
       </c>
       <c r="C60">
-        <v>82</v>
+        <v>143</v>
+      </c>
+      <c r="D60" t="s">
+        <v>14</v>
       </c>
       <c r="E60" t="s">
-        <v>55</v>
-      </c>
-      <c r="G60">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="F60" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" t="s">
+        <v>66</v>
       </c>
       <c r="H60">
-        <v>280</v>
+        <v>405</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
-        <v>46167</v>
+        <v>46212</v>
       </c>
       <c r="B61">
-        <v>504</v>
+        <v>534</v>
       </c>
       <c r="C61">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>56</v>
+        <v>41</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H61">
-        <v>343</v>
+        <v>700</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
-        <v>46167</v>
+        <v>46079</v>
       </c>
       <c r="B62">
-        <v>504</v>
+        <v>450</v>
       </c>
       <c r="C62">
-        <v>47</v>
+        <v>208</v>
       </c>
       <c r="E62" t="s">
-        <v>56</v>
-      </c>
-      <c r="G62" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="F62" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62">
+        <v>2</v>
       </c>
       <c r="H62">
-        <v>882</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
-        <v>46175</v>
+        <v>46079</v>
       </c>
       <c r="B63">
-        <v>506</v>
+        <v>450</v>
       </c>
       <c r="C63">
-        <v>19</v>
+        <v>209</v>
       </c>
       <c r="E63" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63">
         <v>4</v>
       </c>
-      <c r="F63" t="s">
-        <v>45</v>
-      </c>
-      <c r="G63" t="s">
-        <v>10</v>
-      </c>
       <c r="H63">
-        <v>357</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
-        <v>46057</v>
+        <v>46079</v>
       </c>
       <c r="B64">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="C64">
-        <v>17</v>
+        <v>210</v>
       </c>
       <c r="E64" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F64" t="s">
-        <v>5</v>
-      </c>
-      <c r="G64" t="s">
-        <v>8</v>
+        <v>14</v>
+      </c>
+      <c r="G64">
+        <v>6</v>
       </c>
       <c r="H64">
-        <v>400</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
-        <v>46060</v>
+        <v>46079</v>
       </c>
       <c r="B65">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="C65">
-        <v>18</v>
+        <v>211</v>
       </c>
       <c r="E65" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F65" t="s">
-        <v>11</v>
-      </c>
-      <c r="G65" t="s">
-        <v>9</v>
+        <v>14</v>
+      </c>
+      <c r="G65">
+        <v>8</v>
       </c>
       <c r="H65">
-        <v>280</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
-        <v>46134</v>
+        <v>46079</v>
       </c>
       <c r="B66">
-        <v>482</v>
-      </c>
-      <c r="C66" t="s">
-        <v>57</v>
+        <v>450</v>
+      </c>
+      <c r="C66">
+        <v>212</v>
       </c>
       <c r="E66" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F66" t="s">
-        <v>58</v>
-      </c>
-      <c r="G66" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="G66">
+        <v>10</v>
       </c>
       <c r="H66">
-        <v>385</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
-        <v>46147</v>
+        <v>46079</v>
       </c>
       <c r="B67">
-        <v>488</v>
-      </c>
-      <c r="C67" t="s">
-        <v>33</v>
+        <v>450</v>
+      </c>
+      <c r="C67">
+        <v>213</v>
       </c>
       <c r="E67" t="s">
-        <v>43</v>
-      </c>
-      <c r="F67">
-        <v>0</v>
-      </c>
-      <c r="G67" t="s">
-        <v>44</v>
+        <v>13</v>
+      </c>
+      <c r="F67" t="s">
+        <v>14</v>
+      </c>
+      <c r="G67">
+        <v>12</v>
       </c>
       <c r="H67">
-        <v>450</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
-        <v>46151</v>
+        <v>46079</v>
       </c>
       <c r="B68">
-        <v>492</v>
+        <v>451</v>
       </c>
       <c r="C68">
-        <v>80</v>
+        <v>208</v>
       </c>
       <c r="E68" t="s">
-        <v>22</v>
-      </c>
-      <c r="F68">
-        <v>0</v>
-      </c>
-      <c r="G68" t="s">
-        <v>23</v>
+        <v>13</v>
+      </c>
+      <c r="F68" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68">
+        <v>2</v>
       </c>
       <c r="H68">
-        <v>300</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
-        <v>46154</v>
+        <v>46079</v>
       </c>
       <c r="B69">
-        <v>495</v>
+        <v>451</v>
       </c>
       <c r="C69">
-        <v>19</v>
+        <v>209</v>
       </c>
       <c r="E69" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69">
         <v>4</v>
       </c>
-      <c r="F69" t="s">
-        <v>45</v>
-      </c>
-      <c r="G69" t="s">
-        <v>10</v>
-      </c>
       <c r="H69">
-        <v>447</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
-        <v>46156</v>
+        <v>46079</v>
       </c>
       <c r="B70">
-        <v>496</v>
+        <v>451</v>
       </c>
       <c r="C70">
-        <v>41</v>
+        <v>210</v>
       </c>
       <c r="E70" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F70" t="s">
-        <v>18</v>
-      </c>
-      <c r="G70" t="s">
-        <v>9</v>
+        <v>14</v>
+      </c>
+      <c r="G70">
+        <v>6</v>
       </c>
       <c r="H70">
-        <v>400</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
-        <v>46151</v>
+        <v>46079</v>
       </c>
       <c r="B71">
-        <v>493</v>
+        <v>451</v>
       </c>
       <c r="C71">
+        <v>211</v>
+      </c>
+      <c r="E71" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" t="s">
+        <v>14</v>
+      </c>
+      <c r="G71">
+        <v>8</v>
+      </c>
+      <c r="H71" s="2">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B72">
+        <v>451</v>
+      </c>
+      <c r="C72">
+        <v>212</v>
+      </c>
+      <c r="E72" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" t="s">
+        <v>14</v>
+      </c>
+      <c r="G72">
+        <v>10</v>
+      </c>
+      <c r="H72">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B73">
+        <v>451</v>
+      </c>
+      <c r="C73">
+        <v>213</v>
+      </c>
+      <c r="E73" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73">
+        <v>12</v>
+      </c>
+      <c r="H73">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B74">
+        <v>500</v>
+      </c>
+      <c r="C74" t="s">
+        <v>26</v>
+      </c>
+      <c r="E74" t="s">
+        <v>35</v>
+      </c>
+      <c r="G74" t="s">
+        <v>36</v>
+      </c>
+      <c r="H74">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B75">
+        <v>500</v>
+      </c>
+      <c r="C75" t="s">
+        <v>27</v>
+      </c>
+      <c r="E75" t="s">
+        <v>35</v>
+      </c>
+      <c r="G75" t="s">
+        <v>36</v>
+      </c>
+      <c r="H75">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>46179</v>
+      </c>
+      <c r="B76">
+        <v>505</v>
+      </c>
+      <c r="C76">
+        <v>28</v>
+      </c>
+      <c r="E76" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" t="s">
+        <v>68</v>
+      </c>
+      <c r="G76" t="s">
+        <v>5</v>
+      </c>
+      <c r="H76">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B77">
+        <v>509</v>
+      </c>
+      <c r="C77" t="s">
+        <v>28</v>
+      </c>
+      <c r="E77" t="s">
+        <v>37</v>
+      </c>
+      <c r="G77" t="s">
+        <v>33</v>
+      </c>
+      <c r="H77">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B78">
+        <v>509</v>
+      </c>
+      <c r="C78" t="s">
+        <v>28</v>
+      </c>
+      <c r="E78" t="s">
+        <v>37</v>
+      </c>
+      <c r="G78" t="s">
+        <v>33</v>
+      </c>
+      <c r="H78">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B79">
+        <v>509</v>
+      </c>
+      <c r="C79" t="s">
+        <v>28</v>
+      </c>
+      <c r="E79" t="s">
+        <v>37</v>
+      </c>
+      <c r="G79" t="s">
+        <v>33</v>
+      </c>
+      <c r="H79">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B80">
+        <v>509</v>
+      </c>
+      <c r="C80" t="s">
+        <v>29</v>
+      </c>
+      <c r="E80" t="s">
+        <v>37</v>
+      </c>
+      <c r="G80" t="s">
+        <v>33</v>
+      </c>
+      <c r="H80">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B81">
+        <v>509</v>
+      </c>
+      <c r="C81" t="s">
+        <v>29</v>
+      </c>
+      <c r="E81" t="s">
+        <v>37</v>
+      </c>
+      <c r="G81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H81">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B82">
+        <v>509</v>
+      </c>
+      <c r="C82" t="s">
+        <v>29</v>
+      </c>
+      <c r="E82" t="s">
+        <v>37</v>
+      </c>
+      <c r="G82" t="s">
+        <v>33</v>
+      </c>
+      <c r="H82">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B83">
+        <v>517</v>
+      </c>
+      <c r="C83">
+        <v>82</v>
+      </c>
+      <c r="E83" t="s">
+        <v>40</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A84" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B84">
+        <v>519</v>
+      </c>
+      <c r="C84" t="s">
+        <v>69</v>
+      </c>
+      <c r="E84" t="s">
+        <v>70</v>
+      </c>
+      <c r="G84" t="s">
+        <v>71</v>
+      </c>
+      <c r="H84">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A85" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B85">
+        <v>519</v>
+      </c>
+      <c r="C85" t="s">
+        <v>69</v>
+      </c>
+      <c r="E85" t="s">
+        <v>70</v>
+      </c>
+      <c r="G85" t="s">
+        <v>71</v>
+      </c>
+      <c r="H85">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A86" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B86">
+        <v>519</v>
+      </c>
+      <c r="C86" t="s">
+        <v>69</v>
+      </c>
+      <c r="E86" t="s">
+        <v>70</v>
+      </c>
+      <c r="G86" t="s">
+        <v>71</v>
+      </c>
+      <c r="H86">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A87" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B87">
+        <v>519</v>
+      </c>
+      <c r="C87" t="s">
+        <v>72</v>
+      </c>
+      <c r="E87" t="s">
+        <v>70</v>
+      </c>
+      <c r="G87" t="s">
+        <v>71</v>
+      </c>
+      <c r="H87">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A88" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B88">
+        <v>519</v>
+      </c>
+      <c r="C88" t="s">
+        <v>72</v>
+      </c>
+      <c r="E88" t="s">
+        <v>70</v>
+      </c>
+      <c r="G88" t="s">
+        <v>71</v>
+      </c>
+      <c r="H88">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A89" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B89">
+        <v>519</v>
+      </c>
+      <c r="C89" t="s">
+        <v>72</v>
+      </c>
+      <c r="E89" t="s">
+        <v>70</v>
+      </c>
+      <c r="G89" t="s">
+        <v>71</v>
+      </c>
+      <c r="H89">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A90" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B90">
+        <v>521</v>
+      </c>
+      <c r="C90">
+        <v>17</v>
+      </c>
+      <c r="E90" t="s">
+        <v>4</v>
+      </c>
+      <c r="F90" t="s">
+        <v>58</v>
+      </c>
+      <c r="G90" t="s">
+        <v>7</v>
+      </c>
+      <c r="H90">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A91" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B91">
+        <v>524</v>
+      </c>
+      <c r="C91">
+        <v>41</v>
+      </c>
+      <c r="E91" t="s">
+        <v>25</v>
+      </c>
+      <c r="G91" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91">
+        <v>447.5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A92" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B92">
+        <v>524</v>
+      </c>
+      <c r="C92">
+        <v>43</v>
+      </c>
+      <c r="E92" t="s">
+        <v>25</v>
+      </c>
+      <c r="G92" t="s">
+        <v>18</v>
+      </c>
+      <c r="H92">
+        <v>447.5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A93" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B93">
+        <v>525</v>
+      </c>
+      <c r="C93">
+        <v>60</v>
+      </c>
+      <c r="E93" t="s">
+        <v>73</v>
+      </c>
+      <c r="G93" t="s">
+        <v>74</v>
+      </c>
+      <c r="H93">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A94" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B94">
+        <v>527</v>
+      </c>
+      <c r="C94" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" t="s">
+        <v>70</v>
+      </c>
+      <c r="G94" t="s">
+        <v>71</v>
+      </c>
+      <c r="H94">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A95" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B95">
+        <v>527</v>
+      </c>
+      <c r="C95" t="s">
+        <v>69</v>
+      </c>
+      <c r="E95" t="s">
+        <v>70</v>
+      </c>
+      <c r="G95" t="s">
+        <v>71</v>
+      </c>
+      <c r="H95">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A96" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B96">
+        <v>527</v>
+      </c>
+      <c r="C96" t="s">
+        <v>69</v>
+      </c>
+      <c r="E96" t="s">
+        <v>70</v>
+      </c>
+      <c r="G96" t="s">
+        <v>71</v>
+      </c>
+      <c r="H96">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A97" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B97">
+        <v>527</v>
+      </c>
+      <c r="C97" t="s">
+        <v>72</v>
+      </c>
+      <c r="E97" t="s">
+        <v>70</v>
+      </c>
+      <c r="G97" t="s">
+        <v>71</v>
+      </c>
+      <c r="H97">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A98" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B98">
+        <v>527</v>
+      </c>
+      <c r="C98" t="s">
+        <v>72</v>
+      </c>
+      <c r="E98" t="s">
+        <v>70</v>
+      </c>
+      <c r="G98" t="s">
+        <v>71</v>
+      </c>
+      <c r="H98">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A99" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B99">
+        <v>527</v>
+      </c>
+      <c r="C99" t="s">
+        <v>72</v>
+      </c>
+      <c r="E99" t="s">
+        <v>70</v>
+      </c>
+      <c r="G99" t="s">
+        <v>71</v>
+      </c>
+      <c r="H99">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A100" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B100">
+        <v>522</v>
+      </c>
+      <c r="C100">
+        <v>27</v>
+      </c>
+      <c r="E100" t="s">
+        <v>15</v>
+      </c>
+      <c r="F100" t="s">
+        <v>31</v>
+      </c>
+      <c r="G100" t="s">
+        <v>12</v>
+      </c>
+      <c r="H100">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A101" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B101">
+        <v>523</v>
+      </c>
+      <c r="C101">
+        <v>30</v>
+      </c>
+      <c r="E101" t="s">
+        <v>15</v>
+      </c>
+      <c r="F101" t="s">
+        <v>31</v>
+      </c>
+      <c r="G101" t="s">
+        <v>6</v>
+      </c>
+      <c r="H101">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A102" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B102">
+        <v>523</v>
+      </c>
+      <c r="C102">
+        <v>32</v>
+      </c>
+      <c r="E102" t="s">
+        <v>15</v>
+      </c>
+      <c r="F102" t="s">
+        <v>31</v>
+      </c>
+      <c r="G102" t="s">
+        <v>8</v>
+      </c>
+      <c r="H102">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A103" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B103">
+        <v>526</v>
+      </c>
+      <c r="C103">
+        <v>15</v>
+      </c>
+      <c r="E103" t="s">
+        <v>4</v>
+      </c>
+      <c r="F103" t="s">
+        <v>59</v>
+      </c>
+      <c r="G103" t="s">
+        <v>11</v>
+      </c>
+      <c r="H103">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A104" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B104">
+        <v>526</v>
+      </c>
+      <c r="C104">
+        <v>17</v>
+      </c>
+      <c r="E104" t="s">
+        <v>4</v>
+      </c>
+      <c r="F104" t="s">
+        <v>59</v>
+      </c>
+      <c r="G104" t="s">
+        <v>7</v>
+      </c>
+      <c r="H104">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A105" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B105">
+        <v>526</v>
+      </c>
+      <c r="C105">
+        <v>18</v>
+      </c>
+      <c r="E105" t="s">
+        <v>4</v>
+      </c>
+      <c r="F105" t="s">
+        <v>59</v>
+      </c>
+      <c r="G105" t="s">
+        <v>8</v>
+      </c>
+      <c r="H105">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A106" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B106">
+        <v>529</v>
+      </c>
+      <c r="C106" t="s">
+        <v>75</v>
+      </c>
+      <c r="E106" t="s">
+        <v>19</v>
+      </c>
+      <c r="F106" t="s">
+        <v>60</v>
+      </c>
+      <c r="G106" t="s">
+        <v>12</v>
+      </c>
+      <c r="H106">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A107" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B107">
+        <v>529</v>
+      </c>
+      <c r="C107" t="s">
+        <v>42</v>
+      </c>
+      <c r="E107" t="s">
+        <v>19</v>
+      </c>
+      <c r="F107" t="s">
+        <v>60</v>
+      </c>
+      <c r="G107" t="s">
+        <v>11</v>
+      </c>
+      <c r="H107">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A108" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B108">
+        <v>529</v>
+      </c>
+      <c r="C108" t="s">
+        <v>46</v>
+      </c>
+      <c r="E108" t="s">
+        <v>19</v>
+      </c>
+      <c r="F108" t="s">
+        <v>60</v>
+      </c>
+      <c r="G108" t="s">
+        <v>6</v>
+      </c>
+      <c r="H108">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A109" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B109">
+        <v>529</v>
+      </c>
+      <c r="C109" t="s">
+        <v>76</v>
+      </c>
+      <c r="E109" t="s">
+        <v>19</v>
+      </c>
+      <c r="F109" t="s">
+        <v>60</v>
+      </c>
+      <c r="G109" t="s">
+        <v>12</v>
+      </c>
+      <c r="H109">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A110" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B110">
+        <v>529</v>
+      </c>
+      <c r="C110" t="s">
+        <v>77</v>
+      </c>
+      <c r="E110" t="s">
+        <v>19</v>
+      </c>
+      <c r="F110" t="s">
+        <v>60</v>
+      </c>
+      <c r="G110" t="s">
+        <v>11</v>
+      </c>
+      <c r="H110">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A111" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B111">
+        <v>529</v>
+      </c>
+      <c r="C111" t="s">
+        <v>78</v>
+      </c>
+      <c r="E111" t="s">
+        <v>19</v>
+      </c>
+      <c r="F111" t="s">
+        <v>60</v>
+      </c>
+      <c r="G111" t="s">
+        <v>6</v>
+      </c>
+      <c r="H111">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A112" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B112">
+        <v>534</v>
+      </c>
+      <c r="C112">
+        <v>46</v>
+      </c>
+      <c r="E112" t="s">
+        <v>41</v>
+      </c>
+      <c r="G112" t="s">
+        <v>8</v>
+      </c>
+      <c r="H112">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A113" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B113">
+        <v>535</v>
+      </c>
+      <c r="C113">
+        <v>29</v>
+      </c>
+      <c r="E113" t="s">
+        <v>15</v>
+      </c>
+      <c r="F113" t="s">
+        <v>79</v>
+      </c>
+      <c r="G113" t="s">
+        <v>11</v>
+      </c>
+      <c r="H113">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A114" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B114">
+        <v>535</v>
+      </c>
+      <c r="C114">
+        <v>30</v>
+      </c>
+      <c r="E114" t="s">
+        <v>15</v>
+      </c>
+      <c r="F114" t="s">
+        <v>79</v>
+      </c>
+      <c r="G114" t="s">
+        <v>6</v>
+      </c>
+      <c r="H114">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A115" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B115">
+        <v>535</v>
+      </c>
+      <c r="C115">
+        <v>31</v>
+      </c>
+      <c r="E115" t="s">
+        <v>15</v>
+      </c>
+      <c r="F115" t="s">
+        <v>79</v>
+      </c>
+      <c r="G115" t="s">
+        <v>7</v>
+      </c>
+      <c r="H115">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A116" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B116">
+        <v>535</v>
+      </c>
+      <c r="C116">
+        <v>32</v>
+      </c>
+      <c r="E116" t="s">
+        <v>15</v>
+      </c>
+      <c r="F116" t="s">
+        <v>79</v>
+      </c>
+      <c r="G116" t="s">
+        <v>8</v>
+      </c>
+      <c r="H116">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A117" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B117">
+        <v>537</v>
+      </c>
+      <c r="C117">
+        <v>82</v>
+      </c>
+      <c r="E117" t="s">
+        <v>40</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A118" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B118">
+        <v>536</v>
+      </c>
+      <c r="C118">
+        <v>14</v>
+      </c>
+      <c r="E118" t="s">
+        <v>4</v>
+      </c>
+      <c r="F118" t="s">
+        <v>58</v>
+      </c>
+      <c r="G118" t="s">
+        <v>5</v>
+      </c>
+      <c r="H118">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A119" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B119">
+        <v>536</v>
+      </c>
+      <c r="C119">
+        <v>15</v>
+      </c>
+      <c r="E119" t="s">
+        <v>4</v>
+      </c>
+      <c r="F119" t="s">
+        <v>58</v>
+      </c>
+      <c r="G119" t="s">
+        <v>11</v>
+      </c>
+      <c r="H119">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A120" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B120">
+        <v>536</v>
+      </c>
+      <c r="C120">
+        <v>16</v>
+      </c>
+      <c r="E120" t="s">
+        <v>4</v>
+      </c>
+      <c r="F120" t="s">
+        <v>58</v>
+      </c>
+      <c r="G120" t="s">
+        <v>6</v>
+      </c>
+      <c r="H120">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A121" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B121">
+        <v>536</v>
+      </c>
+      <c r="C121">
+        <v>17</v>
+      </c>
+      <c r="E121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F121" t="s">
+        <v>58</v>
+      </c>
+      <c r="G121" t="s">
+        <v>7</v>
+      </c>
+      <c r="H121">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A122" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B122">
+        <v>536</v>
+      </c>
+      <c r="C122">
+        <v>18</v>
+      </c>
+      <c r="E122" t="s">
+        <v>4</v>
+      </c>
+      <c r="F122" t="s">
+        <v>58</v>
+      </c>
+      <c r="G122" t="s">
+        <v>8</v>
+      </c>
+      <c r="H122">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A123" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B123">
+        <v>536</v>
+      </c>
+      <c r="C123">
+        <v>19</v>
+      </c>
+      <c r="E123" t="s">
+        <v>4</v>
+      </c>
+      <c r="F123" t="s">
+        <v>58</v>
+      </c>
+      <c r="G123" t="s">
+        <v>9</v>
+      </c>
+      <c r="H123">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A124" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B124">
+        <v>536</v>
+      </c>
+      <c r="C124">
+        <v>17</v>
+      </c>
+      <c r="E124" t="s">
+        <v>4</v>
+      </c>
+      <c r="F124" t="s">
+        <v>58</v>
+      </c>
+      <c r="G124" t="s">
+        <v>7</v>
+      </c>
+      <c r="H124">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A125" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B125">
+        <v>536</v>
+      </c>
+      <c r="C125">
+        <v>18</v>
+      </c>
+      <c r="E125" t="s">
+        <v>4</v>
+      </c>
+      <c r="F125" t="s">
+        <v>58</v>
+      </c>
+      <c r="G125" t="s">
+        <v>8</v>
+      </c>
+      <c r="H125">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A126" s="1">
+        <v>46220</v>
+      </c>
+      <c r="B126">
+        <v>538</v>
+      </c>
+      <c r="C126">
+        <v>188</v>
+      </c>
+      <c r="E126" t="s">
         <v>80</v>
       </c>
-      <c r="E71" t="s">
-        <v>22</v>
-      </c>
-      <c r="F71">
-        <v>0</v>
-      </c>
-      <c r="G71" t="s">
-        <v>23</v>
-      </c>
-      <c r="H71" s="2">
-        <v>300</v>
+      <c r="F126" t="s">
+        <v>14</v>
+      </c>
+      <c r="G126">
+        <v>2</v>
+      </c>
+      <c r="H126">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A127" s="1">
+        <v>46220</v>
+      </c>
+      <c r="B127">
+        <v>538</v>
+      </c>
+      <c r="C127">
+        <v>189</v>
+      </c>
+      <c r="E127" t="s">
+        <v>80</v>
+      </c>
+      <c r="F127" t="s">
+        <v>14</v>
+      </c>
+      <c r="G127">
+        <v>4</v>
+      </c>
+      <c r="H127">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A128" s="1">
+        <v>46220</v>
+      </c>
+      <c r="B128">
+        <v>538</v>
+      </c>
+      <c r="C128">
+        <v>190</v>
+      </c>
+      <c r="E128" t="s">
+        <v>80</v>
+      </c>
+      <c r="F128" t="s">
+        <v>14</v>
+      </c>
+      <c r="G128">
+        <v>6</v>
+      </c>
+      <c r="H128">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A129" s="1">
+        <v>46220</v>
+      </c>
+      <c r="B129">
+        <v>538</v>
+      </c>
+      <c r="C129">
+        <v>191</v>
+      </c>
+      <c r="E129" t="s">
+        <v>80</v>
+      </c>
+      <c r="F129" t="s">
+        <v>14</v>
+      </c>
+      <c r="G129">
+        <v>8</v>
+      </c>
+      <c r="H129">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A130" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B130">
+        <v>540</v>
+      </c>
+      <c r="C130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" t="s">
+        <v>70</v>
+      </c>
+      <c r="G130" t="s">
+        <v>71</v>
+      </c>
+      <c r="H130">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A131" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B131">
+        <v>540</v>
+      </c>
+      <c r="C131" t="s">
+        <v>72</v>
+      </c>
+      <c r="E131" t="s">
+        <v>70</v>
+      </c>
+      <c r="G131" t="s">
+        <v>71</v>
+      </c>
+      <c r="H131">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A132" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B132">
+        <v>540</v>
+      </c>
+      <c r="C132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" t="s">
+        <v>70</v>
+      </c>
+      <c r="G132" t="s">
+        <v>71</v>
+      </c>
+      <c r="H132">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A133" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B133">
+        <v>540</v>
+      </c>
+      <c r="C133" t="s">
+        <v>72</v>
+      </c>
+      <c r="E133" t="s">
+        <v>70</v>
+      </c>
+      <c r="G133" t="s">
+        <v>71</v>
+      </c>
+      <c r="H133">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A134" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B134">
+        <v>540</v>
+      </c>
+      <c r="C134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" t="s">
+        <v>70</v>
+      </c>
+      <c r="G134" t="s">
+        <v>71</v>
+      </c>
+      <c r="H134">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A135" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B135">
+        <v>540</v>
+      </c>
+      <c r="C135" t="s">
+        <v>72</v>
+      </c>
+      <c r="E135" t="s">
+        <v>70</v>
+      </c>
+      <c r="G135" t="s">
+        <v>71</v>
+      </c>
+      <c r="H135">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A136" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B136">
+        <v>539</v>
+      </c>
+      <c r="C136" t="s">
+        <v>81</v>
+      </c>
+      <c r="D136" t="s">
+        <v>82</v>
+      </c>
+      <c r="E136" t="s">
+        <v>19</v>
+      </c>
+      <c r="F136" t="s">
+        <v>83</v>
+      </c>
+      <c r="G136" t="s">
+        <v>5</v>
+      </c>
+      <c r="H136">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A137" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B137">
+        <v>539</v>
+      </c>
+      <c r="C137" t="s">
+        <v>84</v>
+      </c>
+      <c r="E137" t="s">
+        <v>19</v>
+      </c>
+      <c r="F137" t="s">
+        <v>83</v>
+      </c>
+      <c r="G137" t="s">
+        <v>5</v>
+      </c>
+      <c r="H137">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A138" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B138">
+        <v>539</v>
+      </c>
+      <c r="C138" t="s">
+        <v>42</v>
+      </c>
+      <c r="D138" t="s">
+        <v>82</v>
+      </c>
+      <c r="E138" t="s">
+        <v>19</v>
+      </c>
+      <c r="F138" t="s">
+        <v>83</v>
+      </c>
+      <c r="G138" t="s">
+        <v>11</v>
+      </c>
+      <c r="H138">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A139" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B139">
+        <v>539</v>
+      </c>
+      <c r="C139" t="s">
+        <v>77</v>
+      </c>
+      <c r="E139" t="s">
+        <v>19</v>
+      </c>
+      <c r="F139" t="s">
+        <v>83</v>
+      </c>
+      <c r="G139" t="s">
+        <v>11</v>
+      </c>
+      <c r="H139">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A140" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B140">
+        <v>539</v>
+      </c>
+      <c r="C140" t="s">
+        <v>46</v>
+      </c>
+      <c r="D140" t="s">
+        <v>82</v>
+      </c>
+      <c r="E140" t="s">
+        <v>19</v>
+      </c>
+      <c r="F140" t="s">
+        <v>83</v>
+      </c>
+      <c r="G140" t="s">
+        <v>6</v>
+      </c>
+      <c r="H140">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A141" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B141">
+        <v>539</v>
+      </c>
+      <c r="C141" t="s">
+        <v>78</v>
+      </c>
+      <c r="E141" t="s">
+        <v>19</v>
+      </c>
+      <c r="F141" t="s">
+        <v>83</v>
+      </c>
+      <c r="G141" t="s">
+        <v>6</v>
+      </c>
+      <c r="H141">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A142" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B142">
+        <v>539</v>
+      </c>
+      <c r="C142" t="s">
+        <v>53</v>
+      </c>
+      <c r="D142" t="s">
+        <v>82</v>
+      </c>
+      <c r="E142" t="s">
+        <v>19</v>
+      </c>
+      <c r="F142" t="s">
+        <v>83</v>
+      </c>
+      <c r="G142" t="s">
+        <v>7</v>
+      </c>
+      <c r="H142">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A143" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B143">
+        <v>539</v>
+      </c>
+      <c r="C143" t="s">
+        <v>55</v>
+      </c>
+      <c r="E143" t="s">
+        <v>19</v>
+      </c>
+      <c r="F143" t="s">
+        <v>83</v>
+      </c>
+      <c r="G143" t="s">
+        <v>7</v>
+      </c>
+      <c r="H143">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A144" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B144">
+        <v>539</v>
+      </c>
+      <c r="C144" t="s">
+        <v>54</v>
+      </c>
+      <c r="D144" t="s">
+        <v>82</v>
+      </c>
+      <c r="E144" t="s">
+        <v>19</v>
+      </c>
+      <c r="F144" t="s">
+        <v>83</v>
+      </c>
+      <c r="G144" t="s">
+        <v>8</v>
+      </c>
+      <c r="H144">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A145" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B145">
+        <v>539</v>
+      </c>
+      <c r="C145" t="s">
+        <v>47</v>
+      </c>
+      <c r="E145" t="s">
+        <v>19</v>
+      </c>
+      <c r="F145" t="s">
+        <v>83</v>
+      </c>
+      <c r="G145" t="s">
+        <v>8</v>
+      </c>
+      <c r="H145">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A146" s="1">
+        <v>46226</v>
+      </c>
+      <c r="B146">
+        <v>541</v>
+      </c>
+      <c r="C146" t="s">
+        <v>69</v>
+      </c>
+      <c r="E146" t="s">
+        <v>70</v>
+      </c>
+      <c r="G146" t="s">
+        <v>71</v>
+      </c>
+      <c r="H146">
+        <v>113.5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A147" s="1">
+        <v>46226</v>
+      </c>
+      <c r="B147">
+        <v>541</v>
+      </c>
+      <c r="C147" t="s">
+        <v>72</v>
+      </c>
+      <c r="E147" t="s">
+        <v>70</v>
+      </c>
+      <c r="G147" t="s">
+        <v>71</v>
+      </c>
+      <c r="H147">
+        <v>113.5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A148" s="1">
+        <v>46226</v>
+      </c>
+      <c r="B148">
+        <v>541</v>
+      </c>
+      <c r="C148" t="s">
+        <v>69</v>
+      </c>
+      <c r="E148" t="s">
+        <v>70</v>
+      </c>
+      <c r="G148" t="s">
+        <v>71</v>
+      </c>
+      <c r="H148">
+        <v>113.5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A149" s="1">
+        <v>46226</v>
+      </c>
+      <c r="B149">
+        <v>541</v>
+      </c>
+      <c r="C149" t="s">
+        <v>72</v>
+      </c>
+      <c r="E149" t="s">
+        <v>70</v>
+      </c>
+      <c r="G149" t="s">
+        <v>71</v>
+      </c>
+      <c r="H149">
+        <v>113.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A150" s="1">
+        <v>46226</v>
+      </c>
+      <c r="B150">
+        <v>541</v>
+      </c>
+      <c r="C150" t="s">
+        <v>69</v>
+      </c>
+      <c r="E150" t="s">
+        <v>70</v>
+      </c>
+      <c r="G150" t="s">
+        <v>71</v>
+      </c>
+      <c r="H150">
+        <v>113.5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A151" s="1">
+        <v>46226</v>
+      </c>
+      <c r="B151">
+        <v>541</v>
+      </c>
+      <c r="C151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E151" t="s">
+        <v>70</v>
+      </c>
+      <c r="G151" t="s">
+        <v>71</v>
+      </c>
+      <c r="H151">
+        <v>113.5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="G2:G151" twoDigitTextYear="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>